--- a/tests/workbooktests/workbooks/test_dividends.xlsx
+++ b/tests/workbooktests/workbooks/test_dividends.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95F6F1B6-2E2F-48C2-8E46-4FACDF124FDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7344861-90EF-4265-A64A-9144F1683D99}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{0C387F45-4188-46D7-BB29-3B0CE3AA2B19}"/>
   </bookViews>
@@ -20,17 +20,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -39,14 +28,14 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
       <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+        <ext xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
           <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
         </ext>
       </extLst>
@@ -61,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="7">
   <si>
     <t>Date</t>
   </si>
@@ -79,13 +68,16 @@
   </si>
   <si>
     <t>qlDividendVector</t>
+  </si>
+  <si>
+    <t>{=qlDividendVector(B10:B12;C10:C12)}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -114,12 +106,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -451,15 +444,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A12A55D0-2898-40E2-B56E-54043A13B337}">
-  <dimension ref="A2:D15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:D14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="25.33203125" customWidth="1"/>
-    <col min="2" max="2" width="39.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.375" customWidth="1"/>
+    <col min="2" max="2" width="44.25" customWidth="1"/>
+    <col min="3" max="3" width="10.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -467,7 +460,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -475,7 +468,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -483,7 +476,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4">
       <c r="C6" t="s">
         <v>0</v>
       </c>
@@ -491,7 +484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -508,7 +501,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -521,7 +514,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4">
       <c r="B10" s="1">
         <v>46174</v>
       </c>
@@ -529,7 +522,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4">
       <c r="B11" s="1">
         <f>B10+365</f>
         <v>46539</v>
@@ -538,7 +531,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4">
       <c r="B12" s="1">
         <f>B11+365</f>
         <v>46904</v>
@@ -547,23 +540,18 @@
         <v>80</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
         <v>5</v>
       </c>
-      <c r="B13" t="str" cm="1">
-        <f t="array" ref="B13:B15">_xll.qlDividendVector(B10:B12,C10:C12)</f>
+      <c r="B13" t="str">
+        <f>_xll.qlDividendVector(B10:B12,C10:C12)</f>
         <v>欣[test_dividends.xlsx]Sheet1!R13C2Dividend,A</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B14" t="str">
-        <v>欣[test_dividends.xlsx]Sheet1!R13C2Dividend,B</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B15" t="str">
-        <v>欣[test_dividends.xlsx]Sheet1!R13C2Dividend,C</v>
+    <row r="14" spans="1:4">
+      <c r="B14" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
